--- a/campus-tests/SIT Master/Aptitude/set5_hard.xlsx
+++ b/campus-tests/SIT Master/Aptitude/set5_hard.xlsx
@@ -702,32 +702,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>easy</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Find the next number in the series: 5, 10, 20, 40, ?</t>
+          <t>Find the next number in the series: 2, 3, 7, 16, 32, ?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -887,27 +887,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Find the next number in the series: 100, 93, 86, 79, ?</t>
+          <t>Find the next number in the series: 2, 3, 5, 7, 11, 13, ?</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
